--- a/data/trans_dic/P25C_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 6,24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,84</t>
+          <t>0,34; 4,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 8,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,58</t>
+          <t>2,52; 14,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,97</t>
+          <t>1,53; 7,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,71</t>
+          <t>0,3; 2,79</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,79</t>
+          <t>1,0; 10,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,22</t>
+          <t>0,77; 7,73</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,04</t>
+          <t>0,63; 6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,91</t>
+          <t>2,53; 10,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,02</t>
+          <t>2,04; 6,74</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,65</t>
+          <t>0,17; 6,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,8</t>
+          <t>1,68; 15,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,5</t>
+          <t>0,28; 6,53</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,84</t>
+          <t>0,64; 2,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,87</t>
+          <t>2,36; 5,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,32</t>
+          <t>1,12; 3,33</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 4080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3725</t>
+          <t>0; 3720</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6324</t>
+          <t>0; 4821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>600; 8512</t>
+          <t>597; 7379</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5629</t>
+          <t>0; 5524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1246; 7218</t>
+          <t>1248; 7337</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1903; 9428</t>
+          <t>1807; 9133</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>0; 3579</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 2909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>439; 4139</t>
+          <t>454; 4255</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 753</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 941</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>460; 4441</t>
+          <t>453; 4837</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>455; 4634</t>
+          <t>434; 4361</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>766; 8577</t>
+          <t>765; 7976</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2212; 9395</t>
+          <t>2403; 10153</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4577; 15207</t>
+          <t>4416; 14606</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>445; 23011</t>
+          <t>587; 22466</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>618; 5630</t>
+          <t>637; 5937</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1512; 24966</t>
+          <t>1094; 25088</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4998; 24125</t>
+          <t>5471; 23595</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8274; 19798</t>
+          <t>7949; 19165</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13092; 39386</t>
+          <t>13243; 39568</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,58</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,19</t>
+          <t>0,33; 3,64</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 6,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,82</t>
+          <t>2,51; 14,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,72</t>
+          <t>1,5; 7,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,79</t>
+          <t>0,28; 2,43</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,66</t>
+          <t>1,1; 10,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,73</t>
+          <t>0,89; 8,55</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,55</t>
+          <t>0,59; 6,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,71</t>
+          <t>2,58; 10,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,74</t>
+          <t>2,14; 6,34</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,49</t>
+          <t>2,5; 10,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,61</t>
+          <t>1,62; 14,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,53</t>
+          <t>3,2; 9,52</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,78</t>
+          <t>1,4; 3,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,68</t>
+          <t>2,51; 5,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,33</t>
+          <t>2,11; 3,91</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>0; 3115</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2276</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4821</t>
+          <t>0; 5163</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3938</t>
+          <t>0; 4093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>597; 7379</t>
+          <t>609; 6748</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4524</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5524</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1248; 7337</t>
+          <t>1244; 7415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1807; 9133</t>
+          <t>1760; 8759</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1582</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>0; 3185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2909</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>454; 4255</t>
+          <t>477; 4190</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>453; 4837</t>
+          <t>489; 4614</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>434; 4361</t>
+          <t>500; 4792</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>9651</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>765; 7976</t>
+          <t>844; 8810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2403; 10153</t>
+          <t>2775; 11551</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4416; 14606</t>
+          <t>5344; 15824</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8883</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>587; 22466</t>
+          <t>2837; 12120</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>637; 5937</t>
+          <t>719; 6492</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1094; 25088</t>
+          <t>5052; 15020</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5471; 23595</t>
+          <t>9227; 23473</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7949; 19165</t>
+          <t>9192; 21380</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13243; 39568</t>
+          <t>21661; 40124</t>
         </is>
       </c>
     </row>
